--- a/NPS.xlsx
+++ b/NPS.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rc315bd28be6c4e5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R24fbffd28a39447a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8868,18 +8868,66 @@
           <x:t>Pagamento e questões financeiras,Entrega de Produtos,Aplicativo BEES</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>A equipe de entrega é profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil resolver problemas de pagamento</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>É Fácil encontrar a quantidade de produtos que preciso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -9066,18 +9114,66 @@
           <x:t>Relacionamento com o Vendedor ou com o time Comercial</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -9264,18 +9360,66 @@
           <x:t>Entrega de Produtos,Materiais e equipamentos [geladeira, mesa, cadeira]</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As entregas chegam com atraso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -9462,18 +9606,66 @@
           <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preços são atrativos no BEES, Os preços no app são fáceis de entender, As condições das promoções são fáceis de entender, As Promoções valem a pena</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Dias de entrega disponíveis são bons, Meus pedidos chegam completos, A equipe de entrega é profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Estou satisfeito com meu limite de crédito, Fácil resolver problemas de pagamento, O prazo de pagamento me atende, Entendo as taxas financeiras no pagamento a prazo, Formas de pagamento disponíveis são boas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil localizar produtos, É Fácil encontrar a quantidade de produtos que preciso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As ofertas de pontos são fáceis de entender, As ofertas de pontos valem a pena, Os pontos são atribuídos ou reembolsados corretamente, Itens resgatados foram entregues como esperado, Satisfeito com as opções de itens para resgate</x:t>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -9559,18 +9751,66 @@
           <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Estou satisfeito com meu limite de crédito</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -9656,18 +9896,66 @@
           <x:t>Relacionamento com o Vendedor ou com o time Comercial,Suporte Ambev</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendedor explica novidades úteis de produtos e do app BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -9753,18 +10041,66 @@
           <x:t>Relacionamento com o Vendedor ou com o time Comercial</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c t="inlineStr">
         <x:is>
@@ -9854,18 +10190,66 @@
           <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Suporte Ambev,Materiais e equipamentos [geladeira, mesa, cadeira],Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Sei o preço sugerido ao consumidor, Preço final igual ao mostrado no Bees, Preços são atrativos no BEES, Os preços no app são fáceis de entender, As condições das promoções são fáceis de entender, As Promoções valem a pena</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Recebi o material estrutural solicitado  (mesa, cadeira, etc.), Manutenção de equipamentos é eficiente, Recebi o equipamento de refrigeração solicitado, Entendo as regras para receber equipamento de refrigeração, Entendo como receber materiais de apoio (cartaz, cervegela, etc.), Recebi o material de apoio solicitado (cartaz, cervegela, etc.)</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Dias de entrega disponíveis são bons, Consigo acompanhar o status da entrega, Fácil resolver problemas com produtos entregues danificados, Meus pedidos chegam completos, As entregas chegam no prazo, A equipe de entrega é profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Estou satisfeito com meu limite de crédito, Fácil resolver problemas de pagamento, O prazo de pagamento me atende, Entendo as taxas financeiras no pagamento a prazo, Formas de pagamento disponíveis são boas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O app BEES é rápido, Notificações do app Bees são úteis, BEES recomenda produtos relevantes, Fácil localizar produtos, É fácil atualizar ou cancelar pedidos, É Fácil encontrar a quantidade de produtos que preciso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O atendente do 0800 me ajuda a resolver problemas, É fácil acompanhar o status das minhas solicitações, Eu não preciso de ajuda para abrir uma solicitação, Eu sei que há suporte disponível no app, Minhas solicitações são resolvidas com sucesso, Minhas solicitações são resolvidas em um tempo satisfatório</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As ofertas de pontos são fáceis de entender, As ofertas de pontos valem a pena, Os itens para resgate têm um valor justo, Os pontos são atribuídos ou reembolsados corretamente, Itens resgatados foram entregues como esperado, Satisfeito com as opções de itens para resgate</x:t>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c t="inlineStr">
         <x:is>
@@ -9955,18 +10339,66 @@
           <x:t>Relacionamento com o Vendedor ou com o time Comercial</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -10052,18 +10484,66 @@
           <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Suporte Ambev,Materiais e equipamentos [geladeira, mesa, cadeira],Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendedor ajuda a resolver problemas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O app BEES é rápido, Fácil localizar produtos, É Fácil encontrar a quantidade de produtos que preciso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c t="inlineStr">
         <x:is>
@@ -10153,18 +10633,66 @@
           <x:t>Relacionamento com o Vendedor ou com o time Comercial</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -10351,18 +10879,66 @@
           <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Suporte Ambev,Materiais e equipamentos [geladeira, mesa, cadeira],Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Sei o preço sugerido ao consumidor, Preço final igual ao mostrado no Bees, Preços são atrativos no BEES, Os preços no app são fáceis de entender, As condições das promoções são fáceis de entender, As Promoções valem a pena</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Recebi o material estrutural solicitado  (mesa, cadeira, etc.), Manutenção de equipamentos é eficiente, Recebi o equipamento de refrigeração solicitado, Entendo as regras para receber equipamento de refrigeração, Entendo como receber materiais de apoio (cartaz, cervegela, etc.), Recebi o material de apoio solicitado (cartaz, cervegela, etc.)</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Dias de entrega disponíveis são bons, Consigo acompanhar o status da entrega, Fácil resolver problemas com produtos entregues danificados, Meus pedidos chegam completos, As entregas chegam no prazo, A equipe de entrega é profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Estou satisfeito com meu limite de crédito, Fácil resolver problemas de pagamento, O prazo de pagamento me atende, Entendo as taxas financeiras no pagamento a prazo, Formas de pagamento disponíveis são boas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O app BEES é rápido, Notificações do app Bees são úteis, BEES recomenda produtos relevantes, Fácil localizar produtos, É fácil atualizar ou cancelar pedidos, É Fácil encontrar a quantidade de produtos que preciso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O atendente do 0800 me ajuda a resolver problemas, É fácil acompanhar o status das minhas solicitações, Eu não preciso de ajuda para abrir uma solicitação, Eu sei que há suporte disponível no app, Minhas solicitações são resolvidas com sucesso, Minhas solicitações são resolvidas em um tempo satisfatório</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As ofertas de pontos são fáceis de entender, As ofertas de pontos valem a pena, Os itens para resgate têm um valor justo, Os pontos são atribuídos ou reembolsados corretamente, Itens resgatados foram entregues como esperado, Satisfeito com as opções de itens para resgate</x:t>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -10448,18 +11024,66 @@
           <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Suporte Ambev,Materiais e equipamentos [geladeira, mesa, cadeira],Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Sei o preço sugerido ao consumidor, Preço final igual ao mostrado no Bees, Preços são atrativos no BEES, Os preços no app são fáceis de entender, As condições das promoções são fáceis de entender, As Promoções valem a pena</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Recebi o material estrutural solicitado  (mesa, cadeira, etc.), Manutenção de equipamentos é eficiente, Recebi o equipamento de refrigeração solicitado, Entendo as regras para receber equipamento de refrigeração, Entendo como receber materiais de apoio (cartaz, cervegela, etc.), Recebi o material de apoio solicitado (cartaz, cervegela, etc.)</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Dias de entrega disponíveis são bons, Consigo acompanhar o status da entrega, Fácil resolver problemas com produtos entregues danificados, Meus pedidos chegam completos, As entregas chegam no prazo, A equipe de entrega é profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Estou satisfeito com meu limite de crédito, Fácil resolver problemas de pagamento, O prazo de pagamento me atende, Entendo as taxas financeiras no pagamento a prazo, Formas de pagamento disponíveis são boas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O app BEES é rápido, Notificações do app Bees são úteis, BEES recomenda produtos relevantes, Fácil localizar produtos, É fácil atualizar ou cancelar pedidos, É Fácil encontrar a quantidade de produtos que preciso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O atendente do 0800 me ajuda a resolver problemas, É fácil acompanhar o status das minhas solicitações, Eu não preciso de ajuda para abrir uma solicitação, Eu sei que há suporte disponível no app, Minhas solicitações são resolvidas com sucesso, Minhas solicitações são resolvidas em um tempo satisfatório</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As ofertas de pontos são fáceis de entender, As ofertas de pontos valem a pena, Os itens para resgate têm um valor justo, Os pontos são atribuídos ou reembolsados corretamente, Itens resgatados foram entregues como esperado, Satisfeito com as opções de itens para resgate</x:t>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -10545,18 +11169,66 @@
           <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Suporte Ambev,Materiais e equipamentos [geladeira, mesa, cadeira],Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Sei o preço sugerido ao consumidor, Preço final igual ao mostrado no Bees, Preços são atrativos no BEES, Os preços no app são fáceis de entender, As condições das promoções são fáceis de entender, As Promoções valem a pena</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Recebi o material estrutural solicitado  (mesa, cadeira, etc.), Manutenção de equipamentos é eficiente, Recebi o equipamento de refrigeração solicitado, Entendo as regras para receber equipamento de refrigeração, Entendo como receber materiais de apoio (cartaz, cervegela, etc.), Recebi o material de apoio solicitado (cartaz, cervegela, etc.)</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Dias de entrega disponíveis são bons, Consigo acompanhar o status da entrega, Fácil resolver problemas com produtos entregues danificados, Meus pedidos chegam completos, As entregas chegam no prazo, A equipe de entrega é profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Estou satisfeito com meu limite de crédito, Fácil resolver problemas de pagamento, O prazo de pagamento me atende, Entendo as taxas financeiras no pagamento a prazo, Formas de pagamento disponíveis são boas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O app BEES é rápido, Notificações do app Bees são úteis, BEES recomenda produtos relevantes, Fácil localizar produtos, É fácil atualizar ou cancelar pedidos, É Fácil encontrar a quantidade de produtos que preciso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O atendente do 0800 me ajuda a resolver problemas, É fácil acompanhar o status das minhas solicitações, Eu não preciso de ajuda para abrir uma solicitação, Eu sei que há suporte disponível no app, Minhas solicitações são resolvidas com sucesso, Minhas solicitações são resolvidas em um tempo satisfatório</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As ofertas de pontos são fáceis de entender, As ofertas de pontos valem a pena, Os itens para resgate têm um valor justo, Os pontos são atribuídos ou reembolsados corretamente, Itens resgatados foram entregues como esperado, Satisfeito com as opções de itens para resgate</x:t>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -10776,6 +11448,2212 @@
       <x:c t="inlineStr">
         <x:is>
           <x:t>3157178</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-04 06:42:17</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial,Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As Promoções valem a pena</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor explica novidades úteis de produtos e do app BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MARACAJU</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VISTA ALEGRE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111068261</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3141341</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-04 06:58:56</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCEARIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial,Aplicativo BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendedor ajuda a resolver problemas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Score 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BATAGUASSU</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JARDIM SANTA ROSA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111059621</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3150066</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-04 10:30:39</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCEARIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Aplicativo BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendedor com postura profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BATAGUASSU</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JARDIM ACAPULCO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111094552</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3147171</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-04 13:26:40</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial,Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MARACAJU</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VILA JUQUITA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111071793</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3153768</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-04 15:11:15</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCEARIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>neutro</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Entrega de Produtos</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>A equipe de entrega é pouco profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Melhorar entregadores já aconteceu entregarem pedidos errados</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADINA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VILA VARGAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111045972</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3140985</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-04 15:23:13</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>detrator</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Entrega de Produtos,Preços e Promoções</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Dias de entrega disponíveis não são bons, As entregas chegam com atraso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Monte de avaria nas brahmas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Score 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Indefinido</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111132339</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3143541</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-04 20:27:48</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Suporte Ambev,Aplicativo BEES,Programa de Pontos</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O app BEES é rápido, Notificações do app Bees são úteis, BEES recomenda produtos relevantes, Fácil localizar produtos, É fácil atualizar ou cancelar pedidos, É Fácil encontrar a quantidade de produtos que preciso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Minhas solicitações são resolvidas com sucesso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BATAGUASSU</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111030795</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3158709</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-05 05:31:12</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NÃO DEFINIDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>detrator</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preços e Promoções</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CAMPO DOURADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110914185</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3158922</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-05 05:48:06</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Aplicativo BEES,Programa de Pontos</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ANGELICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IPEZAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110955649</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3159353</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-05 05:56:55</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUBDISTRIBUIDOR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial,Suporte Ambev</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>AMAMBAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VILA CRISTINA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110936668</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3156256</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-05 05:58:50</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LANCHONETE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Aplicativo BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DEODAPOLIS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111071471</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3141651</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-05 06:27:54</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LANCHONETE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Suporte Ambev,Materiais e equipamentos [geladeira, mesa, cadeira],Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preços são atrativos no BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendedor ajuda a resolver problemas, Vendedor com postura profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Meus pedidos chegam completos</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Estou satisfeito com meu limite de crédito</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BEES recomenda produtos relevantes</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>É fácil acompanhar o status das minhas solicitações</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As ofertas de pontos são fáceis de entender</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Não</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JARDIM AMERICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111066931</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3147638</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-05 06:52:02</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Suporte Ambev,Materiais e equipamentos [geladeira, mesa, cadeira],Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SITIOCA CAMPINA VERD</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110972567</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3141925</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-05 07:10:47</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCEARIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DEODAPOLIS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Indefinido</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111115575</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3158932</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-05 07:31:57</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PONTA PORA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JARDIM PRIMAVERA I</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111078830</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3141709</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-06 08:13:55</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Suporte Ambev,Materiais e equipamentos [geladeira, mesa, cadeira],Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PANAMBI VERA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111111659</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3149266</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-07 08:17:31</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LANCHONETE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>neutro</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Materiais e equipamentos [geladeira, mesa, cadeira]</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NAVIRAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111113142</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3153890</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-07 16:12:11</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LANCHONETE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Pagamento e questões financeiras</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NAVIRAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111033781</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3153698</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/NPS.xlsx
+++ b/NPS.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R24fbffd28a39447a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rddec980a0fdf4639"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13520,18 +13520,66 @@
           <x:t>Materiais e equipamentos [geladeira, mesa, cadeira]</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Não recebi o material estrutural solicitado  (mesa, cadeira, etc.), Não entendo como receber materiais de apoio (cartaz, cervegela, etc.)</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -13654,6 +13702,701 @@
       <x:c t="inlineStr">
         <x:is>
           <x:t>3153698</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-08 06:05:47</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>OUTROS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Aplicativo BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Score 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IVINHEMA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>POLO EMP ALBINO MANICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111056067</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3145275</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-08 07:07:05</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GLORIA DE DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111129698</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3148727</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-08 07:36:13</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Aplicativo BEES,Programa de Pontos</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ANTONIO JOAO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VILA PENZO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111046049</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3150965</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-08 07:45:29</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RESTAURANTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Aplicativo BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ANTONIO JOAO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VILA ARABELA FREIRE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110919714</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3158670</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-08 09:03:05</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ACOUGUE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Aplicativo BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JARDIM AGUA BOA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110946508</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3159786</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-08 11:34:40</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LANCHONETE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>neutro</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Entrega de Produtos</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JARDIM PAULISTA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111105285</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3143863</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-08 12:09:01</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PONTA PORA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JARDIM SAO JOAO 1 SECAO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110967573</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3142989</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -13663,6 +14406,7 @@
         <x:is>
           <x:t>Filtros aplicados:
 dado é Rota
+sigla_uf_operacao é MS
 ano é 2026
 tipo_operacao é REVENDA
 grupo_revenda é GRAN DOURADOS

--- a/NPS.xlsx
+++ b/NPS.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rddec980a0fdf4639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R8391d26486e84a6b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2035,7 +2035,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>NÃO DEFINIDA</x:t>
+          <x:t>MERCADO</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -13863,18 +13863,66 @@
           <x:t>Relacionamento com o Vendedor ou com o time Comercial</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c t="inlineStr">
         <x:is>
@@ -13964,18 +14012,66 @@
           <x:t>Aplicativo BEES,Programa de Pontos</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>É fácil atualizar ou cancelar pedidos</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As ofertas de pontos são fáceis de entender</x:t>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c t="inlineStr">
         <x:is>
@@ -14065,18 +14161,66 @@
           <x:t>Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Aplicativo BEES</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Consigo acompanhar o status da entrega</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil localizar produtos</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -14162,18 +14306,66 @@
           <x:t>Aplicativo BEES</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>É Fácil encontrar a quantidade de produtos que preciso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -14356,18 +14548,66 @@
           <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
         </x:is>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendedor ajuda a resolver problemas, Vendedor com postura profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c t="inlineStr">
         <x:is>
@@ -14397,6 +14637,592 @@
       <x:c t="inlineStr">
         <x:is>
           <x:t>3142989</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-09 05:51:21</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>FARMACIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Entrega de Produtos,Suporte Ambev,Materiais e equipamentos [geladeira, mesa, cadeira],Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CHACARA CIDELIS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110973282</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3148552</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-09 07:16:57</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>FATIMA DO SUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PIONEIRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110995449</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3146314</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-09 11:34:53</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LANCHONETE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Entrega de Produtos</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JARDIM AGUA BOA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110925802</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3159937</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-09 11:35:40</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>OUTROS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>neutro</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preços e Promoções</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ITAQUIRAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111039149</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3159945</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-09 12:31:56</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial,Suporte Ambev</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>AMAMBAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111068170</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3141103</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-09 13:05:46</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Pagamento e questões financeiras,Relacionamento com o Vendedor ou com o time Comercial,Suporte Ambev,Materiais e equipamentos [geladeira, mesa, cadeira],Aplicativo BEES,Programa de Pontos,Preços e Promoções</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>AMAMBAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111010937</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3141818</x:t>
         </x:is>
       </x:c>
     </x:row>
